--- a/BusinessAnalysis/ambiguity_queries.xlsx
+++ b/BusinessAnalysis/ambiguity_queries.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Micro2Move\BusinessAnalysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2152BE24-D966-48A1-A9FB-7A88A7CED164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23258" windowHeight="12458"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="71">
   <si>
     <t>ID</t>
   </si>
@@ -218,9 +219,6 @@
     <t>We can use: Affordable Reliable Safe</t>
   </si>
   <si>
-    <t>Splash Scree Carousel</t>
-  </si>
-  <si>
     <t>Landing page  branding</t>
   </si>
   <si>
@@ -310,9 +308,6 @@
     <t>Selfie validation</t>
   </si>
   <si>
-    <t>We keep this features ony in production and assume user does not wear dark glasses or hats while taling selfie during MVP</t>
-  </si>
-  <si>
     <t>Create password verification</t>
   </si>
   <si>
@@ -370,12 +365,33 @@
   <si>
     <t xml:space="preserve">Need this information to proceed </t>
   </si>
+  <si>
+    <t>We keep this features only in production and assume user does not wear dark glasses or hats while taking selfie during MVP</t>
+  </si>
+  <si>
+    <t>Splash Screen Carousel</t>
+  </si>
+  <si>
+    <t>1.10</t>
+  </si>
+  <si>
+    <t>Sign Up</t>
+  </si>
+  <si>
+    <t>1.11</t>
+  </si>
+  <si>
+    <t>Do we validate that the user's age is above or equal to 16 while registration (sign up) process?</t>
+  </si>
+  <si>
+    <t>Do we validate that the user's age matches the KYC document's age while registration (sign up) process?</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -409,6 +425,12 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -467,7 +489,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -504,6 +526,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -789,36 +823,36 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L44"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.53125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.21875" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.33203125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="46.53125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="9.86328125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="6.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="32.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="46.5546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="6.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="32.44140625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="43.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C1" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E1" s="12" t="s">
         <v>15</v>
@@ -845,11 +879,11 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="14">
         <v>1.1000000000000001</v>
       </c>
       <c r="C2" s="7"/>
@@ -879,11 +913,11 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="99.75" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="14">
         <v>1.1000000000000001</v>
       </c>
       <c r="C3" s="7"/>
@@ -913,11 +947,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="114" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="14">
         <v>1.1000000000000001</v>
       </c>
       <c r="C4" s="7"/>
@@ -925,10 +959,10 @@
         <v>12</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G4" s="10"/>
       <c r="H4" s="7" t="s">
@@ -944,14 +978,14 @@
         <v>5</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="42.75" x14ac:dyDescent="0.45">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="14">
         <v>1.2</v>
       </c>
       <c r="C5" s="7"/>
@@ -959,10 +993,10 @@
         <v>12</v>
       </c>
       <c r="E5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>27</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>28</v>
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="7" t="s">
@@ -978,25 +1012,25 @@
         <v>5</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="99.75" x14ac:dyDescent="0.45">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>29</v>
+      <c r="B6" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E6" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>30</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>31</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="7" t="s">
@@ -1012,14 +1046,14 @@
         <v>5</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>6</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="14">
         <v>1.4</v>
       </c>
       <c r="C7" s="7"/>
@@ -1027,10 +1061,10 @@
         <v>12</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G7" s="10"/>
       <c r="H7" s="7" t="s">
@@ -1046,14 +1080,14 @@
         <v>5</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>7</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="14">
         <v>1.4</v>
       </c>
       <c r="C8" s="7"/>
@@ -1061,10 +1095,10 @@
         <v>12</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="7" t="s">
@@ -1080,14 +1114,14 @@
         <v>5</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>8</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="14">
         <v>1.4</v>
       </c>
       <c r="C9" s="7"/>
@@ -1095,10 +1129,10 @@
         <v>12</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G9" s="10"/>
       <c r="H9" s="7" t="s">
@@ -1114,23 +1148,23 @@
         <v>5</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="128.25" x14ac:dyDescent="0.45">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
-      <c r="B10" s="7">
+      <c r="B10" s="14">
         <v>1.4</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>61</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>63</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="7" t="s">
@@ -1140,20 +1174,20 @@
         <v>19</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>5</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>9</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="14">
         <v>1.5</v>
       </c>
       <c r="C11" s="7"/>
@@ -1161,10 +1195,10 @@
         <v>12</v>
       </c>
       <c r="E11" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="9" t="s">
         <v>38</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>39</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="7" t="s">
@@ -1180,14 +1214,14 @@
         <v>5</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="71.25" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>10</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="14">
         <v>1.5</v>
       </c>
       <c r="C12" s="7"/>
@@ -1195,10 +1229,10 @@
         <v>12</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G12" s="10"/>
       <c r="H12" s="7" t="s">
@@ -1214,14 +1248,14 @@
         <v>5</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="57" x14ac:dyDescent="0.45">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>11</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="15">
         <v>1.5</v>
       </c>
       <c r="C13" s="3"/>
@@ -1229,10 +1263,10 @@
         <v>12</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="3" t="s">
@@ -1248,14 +1282,14 @@
         <v>5</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="42.75" x14ac:dyDescent="0.45">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>12</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="15">
         <v>1.5</v>
       </c>
       <c r="C14" s="3"/>
@@ -1263,10 +1297,10 @@
         <v>12</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="3" t="s">
@@ -1282,14 +1316,14 @@
         <v>5</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="57" x14ac:dyDescent="0.45">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>13</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="15">
         <v>1.5</v>
       </c>
       <c r="C15" s="3"/>
@@ -1297,10 +1331,10 @@
         <v>12</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="3" t="s">
@@ -1316,14 +1350,14 @@
         <v>5</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>14</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="15">
         <v>1.5</v>
       </c>
       <c r="C16" s="3"/>
@@ -1331,10 +1365,10 @@
         <v>12</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="3" t="s">
@@ -1350,14 +1384,14 @@
         <v>5</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>15</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="15">
         <v>1.5</v>
       </c>
       <c r="C17" s="3"/>
@@ -1365,10 +1399,10 @@
         <v>12</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="3" t="s">
@@ -1384,25 +1418,25 @@
         <v>5</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>16</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>29</v>
+      <c r="B18" s="15" t="s">
+        <v>28</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="3" t="s">
@@ -1418,44 +1452,76 @@
         <v>5</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>17</v>
       </c>
-      <c r="B19" s="3">
-        <v>1</v>
+      <c r="B19" s="15" t="s">
+        <v>66</v>
       </c>
       <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="6"/>
+      <c r="D19" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>69</v>
+      </c>
       <c r="G19" s="4"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
+      <c r="H19" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="L19" s="5"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
+    <row r="20" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <v>18</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>68</v>
+      </c>
       <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="6"/>
+      <c r="D20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="G20" s="4"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="L20" s="5"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
+      <c r="B21" s="15"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="5"/>
@@ -1467,9 +1533,9 @@
       <c r="K21" s="3"/>
       <c r="L21" s="5"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
+      <c r="B22" s="15"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="5"/>
@@ -1481,9 +1547,9 @@
       <c r="K22" s="3"/>
       <c r="L22" s="5"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
+      <c r="B23" s="15"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="5"/>
@@ -1495,9 +1561,9 @@
       <c r="K23" s="3"/>
       <c r="L23" s="5"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
+      <c r="B24" s="15"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="5"/>
@@ -1509,9 +1575,9 @@
       <c r="K24" s="3"/>
       <c r="L24" s="5"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
+      <c r="B25" s="15"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="5"/>
@@ -1523,9 +1589,9 @@
       <c r="K25" s="3"/>
       <c r="L25" s="5"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
+      <c r="B26" s="15"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="5"/>
@@ -1537,9 +1603,9 @@
       <c r="K26" s="3"/>
       <c r="L26" s="5"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
+      <c r="B27" s="15"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="5"/>
@@ -1551,9 +1617,9 @@
       <c r="K27" s="3"/>
       <c r="L27" s="5"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
+      <c r="B28" s="15"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="5"/>
@@ -1565,9 +1631,9 @@
       <c r="K28" s="3"/>
       <c r="L28" s="5"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
+      <c r="B29" s="15"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="5"/>
@@ -1579,9 +1645,9 @@
       <c r="K29" s="3"/>
       <c r="L29" s="5"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
+      <c r="B30" s="15"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="5"/>
@@ -1593,9 +1659,9 @@
       <c r="K30" s="3"/>
       <c r="L30" s="5"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
+      <c r="B31" s="15"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="5"/>
@@ -1607,9 +1673,9 @@
       <c r="K31" s="3"/>
       <c r="L31" s="5"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
+      <c r="B32" s="15"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="5"/>
@@ -1621,9 +1687,9 @@
       <c r="K32" s="3"/>
       <c r="L32" s="5"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
+      <c r="B33" s="15"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="5"/>
@@ -1635,9 +1701,9 @@
       <c r="K33" s="3"/>
       <c r="L33" s="5"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
+      <c r="B34" s="15"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="5"/>
@@ -1649,9 +1715,9 @@
       <c r="K34" s="3"/>
       <c r="L34" s="5"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
+      <c r="B35" s="15"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="5"/>
@@ -1663,9 +1729,9 @@
       <c r="K35" s="3"/>
       <c r="L35" s="5"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
+      <c r="B36" s="15"/>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="5"/>
@@ -1677,9 +1743,9 @@
       <c r="K36" s="3"/>
       <c r="L36" s="5"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="3"/>
-      <c r="B37" s="3"/>
+      <c r="B37" s="15"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="5"/>
@@ -1691,9 +1757,9 @@
       <c r="K37" s="3"/>
       <c r="L37" s="5"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
+      <c r="B38" s="15"/>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="5"/>
@@ -1705,9 +1771,9 @@
       <c r="K38" s="3"/>
       <c r="L38" s="5"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
+      <c r="B39" s="15"/>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="5"/>
@@ -1719,9 +1785,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="5"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
+      <c r="B40" s="15"/>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="5"/>
@@ -1733,9 +1799,9 @@
       <c r="K40" s="3"/>
       <c r="L40" s="5"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
-      <c r="B41" s="3"/>
+      <c r="B41" s="15"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="5"/>
@@ -1747,9 +1813,9 @@
       <c r="K41" s="3"/>
       <c r="L41" s="5"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
+      <c r="B42" s="15"/>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="5"/>
@@ -1761,9 +1827,9 @@
       <c r="K42" s="3"/>
       <c r="L42" s="5"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
+      <c r="B43" s="15"/>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="5"/>
@@ -1775,11 +1841,11 @@
       <c r="K43" s="3"/>
       <c r="L43" s="5"/>
     </row>
-    <row r="44" spans="1:12" ht="142.5" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:12" ht="144" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>2</v>
       </c>
-      <c r="B44" s="3"/>
+      <c r="B44" s="15"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="5" t="s">
@@ -1804,6 +1870,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
